--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C1D226B-AD68-4AA6-AF7E-B37660811819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2810CC3B-9F72-419A-AC1F-4D6592C0F4B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="197">
   <si>
     <t>O(n²)</t>
   </si>
@@ -3664,6 +3664,14 @@
   </si>
   <si>
     <t>只递推y半边将奇异回代的向量反转改为LongWord分块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H51.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>逐列带状回代改为固定Laurent核的32系数分块除法</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4121,7 +4129,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -5552,6 +5560,23 @@
         <v>194</v>
       </c>
     </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2810CC3B-9F72-419A-AC1F-4D6592C0F4B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF6B0C4-B01B-4355-A2E3-9066037C183E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="201">
   <si>
     <t>O(n²)</t>
   </si>
@@ -3672,6 +3672,22 @@
   </si>
   <si>
     <t>逐列带状回代改为固定Laurent核的32系数分块除法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H52.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H53.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>融合Euclid同位移更新并加速最高位查找</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>融合Laurent子核四路平移并直接折叠保留半核</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4129,7 +4145,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -5577,6 +5593,40 @@
         <v>196</v>
       </c>
     </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF6B0C4-B01B-4355-A2E3-9066037C183E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3893C9-941E-4748-AFE2-F1F71CD3A4F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="203">
   <si>
     <t>O(n²)</t>
   </si>
@@ -3688,6 +3688,14 @@
   </si>
   <si>
     <t>融合Laurent子核四路平移并直接折叠保留半核</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H54.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将Laurent循环折叠改为仅抽取保留窗口</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4145,7 +4153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -5627,6 +5635,23 @@
         <v>200</v>
       </c>
     </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>202</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3893C9-941E-4748-AFE2-F1F71CD3A4F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94CCE615-24B3-4615-A53F-2E8ED7299E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="205">
   <si>
     <t>O(n²)</t>
   </si>
@@ -3696,6 +3696,14 @@
   </si>
   <si>
     <t>将Laurent循环折叠改为仅抽取保留窗口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H55.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将扩展欧几里得的余式与Bézout行更新改为无分支融合异或</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4153,7 +4161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -5652,6 +5660,23 @@
         <v>202</v>
       </c>
     </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>204</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94CCE615-24B3-4615-A53F-2E8ED7299E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83BFB750-C626-4100-9264-79C4D403F0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="207">
   <si>
     <t>O(n²)</t>
   </si>
@@ -3704,6 +3704,14 @@
   </si>
   <si>
     <t>将扩展欧几里得的余式与Bézout行更新改为无分支融合异或</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H56.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>展开扩展欧几里得成对异或并以单乘积Karatsuba完成Bézout恢复</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4161,7 +4169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -5677,6 +5685,23 @@
         <v>204</v>
       </c>
     </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>206</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83BFB750-C626-4100-9264-79C4D403F0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1AE84E9-3BDB-410B-91CC-B459B8B7D6D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="209">
   <si>
     <t>O(n²)</t>
   </si>
@@ -3712,6 +3712,14 @@
   </si>
   <si>
     <t>展开扩展欧几里得成对异或并以单乘积Karatsuba完成Bézout恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H57.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拆分Karatsuba递归中的固定公共区与边界区</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4169,7 +4177,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -5570,8 +5578,8 @@
       <c r="A82" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B82" s="4" t="s">
-        <v>88</v>
+      <c r="B82" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>192</v>
@@ -5700,6 +5708,23 @@
       </c>
       <c r="E89" s="10" t="s">
         <v>206</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FCB27B6-0C78-4013-95AA-D793858EE009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6775628-9E29-42FD-9565-ADB9FEF1C81F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="209">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3812,6 +3812,14 @@
       </rPr>
       <t>阶段实现</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>y 闭式＋全 1 前缀卷积</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H59.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4269,7 +4277,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -5836,6 +5844,23 @@
         <v>83</v>
       </c>
     </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>207</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541A9EE3-BB67-4650-8083-5007B289F03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51ABC90-0747-4793-949B-EF5BF2699545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="204">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -906,6 +906,14 @@
   </si>
   <si>
     <t>使用无分配迭代 Fibonacci 倍增，B版按 LongWord 并行计算 y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H61.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>化简y前缀窗，B版融合1024系数Laurent叶节点与64位合并</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1338,7 +1346,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -2939,6 +2947,23 @@
         <v>201</v>
       </c>
     </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51ABC90-0747-4793-949B-EF5BF2699545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C8B1CA-54D8-4C20-91B9-8AE60FF8DE1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="3810" yWindow="3810" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="208">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -914,6 +914,22 @@
   </si>
   <si>
     <t>化简y前缀窗，B版融合1024系数Laurent叶节点与64位合并</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H62.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H63.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连续 Fibonacci 降阶，按字提升 Bézout 系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用 half-gcd 分治和快速除法，将 q 降至约 O(n^1.585)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1346,7 +1362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -2964,6 +2980,40 @@
         <v>203</v>
       </c>
     </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C8B1CA-54D8-4C20-91B9-8AE60FF8DE1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629C2E6E-FB29-43A2-8962-EC92674ADDFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3810" yWindow="3810" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="210">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -930,6 +930,14 @@
   </si>
   <si>
     <t>使用 half-gcd 分治和快速除法，将 q 降至约 O(n^1.585)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H64.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Laurent 核三角除法、Newton 求逆和分块 Karatsuba，优化x</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1362,7 +1370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3014,6 +3022,23 @@
         <v>207</v>
       </c>
     </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629C2E6E-FB29-43A2-8962-EC92674ADDFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA61B502-E04B-495A-A3A2-BDDBDBAF15D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="212">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -940,12 +940,20 @@
     <t>Laurent 核三角除法、Newton 求逆和分块 Karatsuba，优化x</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>O(n^1.585)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>利用余式次数界和成对截断乘法，减少q中的无效高位计算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1011,6 +1019,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1034,7 +1051,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1055,6 +1072,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1370,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3022,21 +3042,38 @@
         <v>207</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A97" s="4" t="s">
+    <row r="97" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="B97" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E97" s="4" t="s">
+      <c r="B97" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E97" s="7" t="s">
         <v>209</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA61B502-E04B-495A-A3A2-BDDBDBAF15D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A275D0-E183-42D8-944C-3A7C6BDDE714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="215">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -946,6 +946,18 @@
   </si>
   <si>
     <t>利用余式次数界和成对截断乘法，减少q中的无效高位计算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H65.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H66.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测反射向量相等并复用卷积乘积，优化gen</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1390,7 +1402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3061,7 +3073,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>154</v>
@@ -3074,6 +3086,23 @@
       </c>
       <c r="E98" s="1" t="s">
         <v>211</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A275D0-E183-42D8-944C-3A7C6BDDE714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6059347-16A7-4068-856E-596F4A6EB24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="219">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -958,6 +958,22 @@
   </si>
   <si>
     <t>检测反射向量相等并复用卷积乘积，优化gen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H67.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H68.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>融合Euclid三路更新并复用Karatsuba重组异或，优化q/z</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将对称源卷积进一步拆为两次半长卷积，优化z/gen</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1402,7 +1418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3105,6 +3121,40 @@
         <v>214</v>
       </c>
     </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6059347-16A7-4068-856E-596F4A6EB24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341CEE68-256F-4813-8A7A-CD83E2E178A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="221">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -974,6 +974,14 @@
   </si>
   <si>
     <t>将对称源卷积进一步拆为两次半长卷积，优化z/gen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H69.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仅构造半边Laurent核并直接循环折叠，优化mak及z/gen的核构造</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1418,7 +1426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3155,6 +3163,23 @@
         <v>218</v>
       </c>
     </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341CEE68-256F-4813-8A7A-CD83E2E178A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC020BE-3C57-420B-9AA7-AFAD486FC8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="223">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -982,6 +982,14 @@
   </si>
   <si>
     <t>仅构造半边Laurent核并直接循环折叠，优化mak及z/gen的核构造</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H70.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合并Euclid相邻商项的余式及Bézout更新，减少q中的重复遍历</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1426,7 +1434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3180,6 +3188,23 @@
         <v>220</v>
       </c>
     </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC020BE-3C57-420B-9AA7-AFAD486FC8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF9B292-8284-47EB-BAC2-BA0A89405077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="9600" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="225">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -992,12 +992,20 @@
     <t>合并Euclid相邻商项的余式及Bézout更新，减少q中的重复遍历</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H71.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>利用对称Laurent基变换将两次半长乘法合为一次，优化z/gen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1063,15 +1071,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF0070C0"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1095,7 +1094,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1116,9 +1115,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1434,7 +1430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3070,36 +3066,36 @@
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A96" s="1" t="s">
+      <c r="A96" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E96" s="3" t="s">
+      <c r="B96" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E96" s="4" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="7" t="s">
+      <c r="A97" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B97" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="C97" s="7" t="s">
+      <c r="B97" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D97" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E97" s="7" t="s">
+      <c r="D97" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>209</v>
       </c>
     </row>
@@ -3203,6 +3199,23 @@
       </c>
       <c r="E103" s="1" t="s">
         <v>222</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF9B292-8284-47EB-BAC2-BA0A89405077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD8F4A0-E891-4D85-AFF5-D26ACC2A8FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9600" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="229">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -998,6 +998,22 @@
   </si>
   <si>
     <t>利用对称Laurent基变换将两次半长乘法合为一次，优化z/gen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H73.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H72.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将基变换推广到非对称源，两次长乘法合为一次，优化gen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在卷积64系数小块内融合Karatsuba三乘法，优化z/gen</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1430,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3218,6 +3234,40 @@
         <v>224</v>
       </c>
     </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
